--- a/sprint1/SRS/SRS.xlsx
+++ b/sprint1/SRS/SRS.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WorkShop\Second\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C6D4E3-AE9C-4965-B51B-476B6A2DC998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="SRS" sheetId="1" r:id="rId5"/>
+    <sheet name="SRS" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="65">
   <si>
     <t>SRS_ID</t>
   </si>
@@ -173,48 +182,109 @@
   <si>
     <t>Admin can Delete user account</t>
   </si>
+  <si>
+    <t>User can follow a category</t>
+  </si>
+  <si>
+    <t>user should have notofication when something new added to his followed category</t>
+  </si>
+  <si>
+    <t>Users can navigate between different categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">users can publish articles </t>
+  </si>
+  <si>
+    <t xml:space="preserve">users can upload videos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">users can record voice notes </t>
+  </si>
+  <si>
+    <t>User Features</t>
+  </si>
+  <si>
+    <t>SRS_28</t>
+  </si>
+  <si>
+    <t>SRS_29</t>
+  </si>
+  <si>
+    <t>SRS_30</t>
+  </si>
+  <si>
+    <t>SRS_31</t>
+  </si>
+  <si>
+    <t>SRS_32</t>
+  </si>
+  <si>
+    <t>SRS_33</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
+      <sz val="13"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA4C2F4"/>
         <bgColor rgb="FFA4C2F4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -229,42 +299,84 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="12">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -272,7 +384,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -462,24 +574,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z45"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="27.5"/>
-    <col customWidth="1" min="2" max="2" width="70.25"/>
-    <col customWidth="1" min="3" max="3" width="33.0"/>
-    <col customWidth="1" min="4" max="4" width="31.38"/>
-    <col customWidth="1" min="5" max="5" width="22.38"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="78.21875" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="31.33203125" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,522 +608,692 @@
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+    </row>
+    <row r="2" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+    </row>
+    <row r="14" spans="1:26" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9"/>
+      <c r="S14" s="9"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="9"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
+      <c r="Z14" s="9"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
+      <c r="E17" s="3"/>
+    </row>
+    <row r="18" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
+      <c r="E18" s="3"/>
+    </row>
+    <row r="19" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="s">
+      <c r="E19" s="3"/>
+    </row>
+    <row r="20" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="s">
+      <c r="E21" s="3"/>
+    </row>
+    <row r="22" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="s">
+      <c r="E22" s="3"/>
+    </row>
+    <row r="23" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="s">
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+    </row>
+    <row r="25" spans="1:26" s="10" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="s">
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+    </row>
+    <row r="26" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
+      <c r="E26" s="3"/>
+    </row>
+    <row r="27" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:26" s="10" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="s">
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="P28" s="9"/>
+      <c r="Q28" s="9"/>
+      <c r="R28" s="9"/>
+      <c r="S28" s="9"/>
+      <c r="T28" s="9"/>
+      <c r="U28" s="9"/>
+      <c r="V28" s="9"/>
+      <c r="W28" s="9"/>
+      <c r="X28" s="9"/>
+      <c r="Y28" s="9"/>
+      <c r="Z28" s="9"/>
+    </row>
+    <row r="29" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="s">
+      <c r="E29" s="3"/>
+    </row>
+    <row r="30" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:26" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>51</v>
       </c>
     </row>
+    <row r="33" spans="1:2" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="11"/>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="11"/>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="5"/>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="5"/>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A14:Z14"/>
     <mergeCell ref="A2:Z2"/>
     <mergeCell ref="A25:Z25"/>
     <mergeCell ref="A28:Z28"/>
+    <mergeCell ref="A33:XFD33"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>